--- a/Excel/StartConfig/LocalhostOld/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/LocalhostOld/StartZoneConfig@s.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\GitWeiJing2022\Excel\StartConfig\Beta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\GitWeiJing2022\Excel\StartConfig\LocalhostOld\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="448">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="694" uniqueCount="449">
   <si>
     <t>Id</t>
   </si>
@@ -1425,6 +1425,9 @@
   </si>
   <si>
     <t>WJBeta235</t>
+  </si>
+  <si>
+    <t>WJBeta236</t>
   </si>
 </sst>
 </file>
@@ -1633,12 +1636,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2520,7 +2523,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:I231"/>
+  <dimension ref="A3:I232"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="3" customWidth="1"/>
@@ -6632,7 +6635,24 @@
       <c r="F231" s="6" t="s">
         <v>447</v>
       </c>
-      <c r="G231" s="12"/>
+      <c r="G231" s="12" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="232" spans="3:8">
+      <c r="C232" s="4">
+        <v>236</v>
+      </c>
+      <c r="D232" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E232" s="6">
+        <v>236</v>
+      </c>
+      <c r="F232" s="6" t="s">
+        <v>448</v>
+      </c>
+      <c r="G232" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/StartConfig/LocalhostOld/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/LocalhostOld/StartZoneConfig@s.xlsx
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="694" uniqueCount="449">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="450">
   <si>
     <t>Id</t>
   </si>
@@ -1428,6 +1428,9 @@
   </si>
   <si>
     <t>WJBeta236</t>
+  </si>
+  <si>
+    <t>月光神域</t>
   </si>
 </sst>
 </file>
@@ -1636,12 +1639,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -6652,7 +6655,9 @@
       <c r="F232" s="6" t="s">
         <v>448</v>
       </c>
-      <c r="G232" s="12"/>
+      <c r="G232" s="12" t="s">
+        <v>449</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/StartConfig/LocalhostOld/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/LocalhostOld/StartZoneConfig@s.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\GitWeiJing2022\Excel\StartConfig\Beta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\GitWeiJing2022\Excel\StartConfig\LocalhostOld\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="450">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="697" uniqueCount="451">
   <si>
     <t>Id</t>
   </si>
@@ -1431,6 +1431,9 @@
   </si>
   <si>
     <t>月光神域</t>
+  </si>
+  <si>
+    <t>WJBeta237</t>
   </si>
 </sst>
 </file>
@@ -1639,12 +1642,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2526,7 +2529,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:I232"/>
+  <dimension ref="A3:I233"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="3" customWidth="1"/>
@@ -6659,6 +6662,21 @@
         <v>449</v>
       </c>
     </row>
+    <row r="233" spans="3:8">
+      <c r="C233" s="4">
+        <v>237</v>
+      </c>
+      <c r="D233" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E233" s="6">
+        <v>237</v>
+      </c>
+      <c r="F233" s="6" t="s">
+        <v>450</v>
+      </c>
+      <c r="G233" s="12"/>
+    </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Excel/StartConfig/LocalhostOld/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/LocalhostOld/StartZoneConfig@s.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\GitWeiJing2022\Excel\StartConfig\LocalhostOld\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\GitWeiJing2022\Excel\StartConfig\Beta\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -1642,12 +1642,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/Excel/StartConfig/LocalhostOld/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/LocalhostOld/StartZoneConfig@s.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\GitWeiJing2022\Excel\StartConfig\Beta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\GitWeiJing2022\Excel\StartConfig\LocalhostOld\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="697" uniqueCount="451">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="452">
   <si>
     <t>Id</t>
   </si>
@@ -1434,6 +1434,9 @@
   </si>
   <si>
     <t>WJBeta237</t>
+  </si>
+  <si>
+    <t>霜火之巅</t>
   </si>
 </sst>
 </file>
@@ -1642,12 +1645,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2143,7 +2146,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2181,6 +2184,7 @@
     <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -6675,7 +6679,9 @@
       <c r="F233" s="6" t="s">
         <v>450</v>
       </c>
-      <c r="G233" s="12"/>
+      <c r="G233" s="25" t="s">
+        <v>451</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/StartConfig/LocalhostOld/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/LocalhostOld/StartZoneConfig@s.xlsx
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="452">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="701" uniqueCount="453">
   <si>
     <t>Id</t>
   </si>
@@ -1437,6 +1437,9 @@
   </si>
   <si>
     <t>霜火之巅</t>
+  </si>
+  <si>
+    <t>WJBeta238</t>
   </si>
 </sst>
 </file>
@@ -1645,12 +1648,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2146,7 +2149,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2184,7 +2187,6 @@
     <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2533,7 +2535,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:I233"/>
+  <dimension ref="A3:I234"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="3" customWidth="1"/>
@@ -6679,8 +6681,25 @@
       <c r="F233" s="6" t="s">
         <v>450</v>
       </c>
-      <c r="G233" s="25" t="s">
+      <c r="G233" s="12" t="s">
         <v>451</v>
+      </c>
+    </row>
+    <row r="234" spans="3:8">
+      <c r="C234" s="4">
+        <v>238</v>
+      </c>
+      <c r="D234" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E234" s="6">
+        <v>238</v>
+      </c>
+      <c r="F234" s="6" t="s">
+        <v>452</v>
+      </c>
+      <c r="G234" s="12" t="s">
+        <v>405</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/LocalhostOld/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/LocalhostOld/StartZoneConfig@s.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\GitWeiJing2022\Excel\StartConfig\LocalhostOld\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\GitWeiJing2022\Excel\StartConfig\Beta\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -1648,12 +1648,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/Excel/StartConfig/LocalhostOld/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/LocalhostOld/StartZoneConfig@s.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\GitWeiJing2022\Excel\StartConfig\Beta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\GitWeiJing2022\Excel\StartConfig\LocalhostOld\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="701" uniqueCount="453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="704" uniqueCount="455">
   <si>
     <t>Id</t>
   </si>
@@ -1440,6 +1440,12 @@
   </si>
   <si>
     <t>WJBeta238</t>
+  </si>
+  <si>
+    <t>WJBeta239</t>
+  </si>
+  <si>
+    <t>翡翠之地</t>
   </si>
 </sst>
 </file>
@@ -2535,7 +2541,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:I234"/>
+  <dimension ref="A3:I235"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="3" customWidth="1"/>
@@ -6702,6 +6708,23 @@
         <v>405</v>
       </c>
     </row>
+    <row r="235" spans="3:8">
+      <c r="C235" s="4">
+        <v>239</v>
+      </c>
+      <c r="D235" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E235" s="6">
+        <v>239</v>
+      </c>
+      <c r="F235" s="6" t="s">
+        <v>453</v>
+      </c>
+      <c r="G235" s="12" t="s">
+        <v>454</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Excel/StartConfig/LocalhostOld/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/LocalhostOld/StartZoneConfig@s.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\GitWeiJing2022\Excel\StartConfig\Beta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\GitWeiJing20220362\Excel\StartConfig\LocalhostOld\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="704" uniqueCount="455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="706" uniqueCount="456">
   <si>
     <t>Id</t>
   </si>
@@ -1446,6 +1446,9 @@
   </si>
   <si>
     <t>翡翠之地</t>
+  </si>
+  <si>
+    <t>WJBeta240</t>
   </si>
 </sst>
 </file>
@@ -2541,7 +2544,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:I235"/>
+  <dimension ref="A3:I236"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="3" customWidth="1"/>
@@ -6725,6 +6728,21 @@
         <v>454</v>
       </c>
     </row>
+    <row r="236" spans="3:8">
+      <c r="C236" s="4">
+        <v>240</v>
+      </c>
+      <c r="D236" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E236" s="6">
+        <v>240</v>
+      </c>
+      <c r="F236" s="6" t="s">
+        <v>455</v>
+      </c>
+      <c r="G236" s="12"/>
+    </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Excel/StartConfig/LocalhostOld/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/LocalhostOld/StartZoneConfig@s.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\GitWeiJing20220362\Excel\StartConfig\LocalhostOld\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\GitWeiJing2022\Excel\StartConfig\LocalhostOld\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="706" uniqueCount="456">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="707" uniqueCount="457">
   <si>
     <t>Id</t>
   </si>
@@ -1449,6 +1449,9 @@
   </si>
   <si>
     <t>WJBeta240</t>
+  </si>
+  <si>
+    <t>青野拾光</t>
   </si>
 </sst>
 </file>
@@ -2158,7 +2161,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2196,6 +2199,7 @@
     <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -6741,7 +6745,9 @@
       <c r="F236" s="6" t="s">
         <v>455</v>
       </c>
-      <c r="G236" s="12"/>
+      <c r="G236" s="25" t="s">
+        <v>456</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/StartConfig/LocalhostOld/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/LocalhostOld/StartZoneConfig@s.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\GitWeiJing2022\Excel\StartConfig\Beta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\GitWeiJing2022\Excel\StartConfig\LocalhostOld\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="707" uniqueCount="457">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="709" uniqueCount="458">
   <si>
     <t>Id</t>
   </si>
@@ -1452,6 +1452,9 @@
   </si>
   <si>
     <t>青野拾光</t>
+  </si>
+  <si>
+    <t>WJBeta241</t>
   </si>
 </sst>
 </file>
@@ -2161,7 +2164,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2199,7 +2202,6 @@
     <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2548,7 +2550,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:I236"/>
+  <dimension ref="A3:I237"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="3" customWidth="1"/>
@@ -6745,9 +6747,24 @@
       <c r="F236" s="6" t="s">
         <v>455</v>
       </c>
-      <c r="G236" s="25" t="s">
+      <c r="G236" s="12" t="s">
         <v>456</v>
       </c>
+    </row>
+    <row r="237" spans="3:8">
+      <c r="C237" s="4">
+        <v>241</v>
+      </c>
+      <c r="D237" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E237" s="6">
+        <v>241</v>
+      </c>
+      <c r="F237" s="6" t="s">
+        <v>457</v>
+      </c>
+      <c r="G237" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/StartConfig/LocalhostOld/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/LocalhostOld/StartZoneConfig@s.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\GitWeiJing2022\Excel\StartConfig\LocalhostOld\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\GitWeiJing2022\Excel\StartConfig\Beta\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="709" uniqueCount="458">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="459">
   <si>
     <t>Id</t>
   </si>
@@ -1455,6 +1455,9 @@
   </si>
   <si>
     <t>WJBeta241</t>
+  </si>
+  <si>
+    <t>逐光之路</t>
   </si>
 </sst>
 </file>
@@ -2164,7 +2167,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2202,6 +2205,7 @@
     <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -6764,7 +6768,9 @@
       <c r="F237" s="6" t="s">
         <v>457</v>
       </c>
-      <c r="G237" s="12"/>
+      <c r="G237" s="25" t="s">
+        <v>458</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/StartConfig/LocalhostOld/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/LocalhostOld/StartZoneConfig@s.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\GitWeiJing2022\Excel\StartConfig\Beta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\GitWeiJing2022\Excel\StartConfig\LocalhostOld\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="459">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="712" uniqueCount="460">
   <si>
     <t>Id</t>
   </si>
@@ -1458,6 +1458,9 @@
   </si>
   <si>
     <t>逐光之路</t>
+  </si>
+  <si>
+    <t>WJBeta242</t>
   </si>
 </sst>
 </file>
@@ -1666,12 +1669,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2167,7 +2170,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2205,7 +2208,6 @@
     <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2554,7 +2556,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:I237"/>
+  <dimension ref="A3:I238"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="3" customWidth="1"/>
@@ -6768,9 +6770,24 @@
       <c r="F237" s="6" t="s">
         <v>457</v>
       </c>
-      <c r="G237" s="25" t="s">
+      <c r="G237" s="12" t="s">
         <v>458</v>
       </c>
+    </row>
+    <row r="238" spans="3:8">
+      <c r="C238" s="4">
+        <v>242</v>
+      </c>
+      <c r="D238" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E238" s="6">
+        <v>242</v>
+      </c>
+      <c r="F238" s="6" t="s">
+        <v>459</v>
+      </c>
+      <c r="G238" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/StartConfig/LocalhostOld/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/LocalhostOld/StartZoneConfig@s.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\GitWeiJing2022\Excel\StartConfig\LocalhostOld\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\GitWeiJing2022\Excel\StartConfig\Beta\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -1669,12 +1669,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/Excel/StartConfig/LocalhostOld/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/LocalhostOld/StartZoneConfig@s.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\GitWeiJing2022\Excel\StartConfig\Beta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\GitWeiJing2022\Excel\StartConfig\LocalhostOld\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="712" uniqueCount="460">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="713" uniqueCount="461">
   <si>
     <t>Id</t>
   </si>
@@ -1461,6 +1461,9 @@
   </si>
   <si>
     <t>WJBeta242</t>
+  </si>
+  <si>
+    <t>苍风之誓</t>
   </si>
 </sst>
 </file>
@@ -6787,7 +6790,9 @@
       <c r="F238" s="6" t="s">
         <v>459</v>
       </c>
-      <c r="G238" s="12"/>
+      <c r="G238" s="12" t="s">
+        <v>460</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
